--- a/output/pdf_financials_xlsx/GFM.H.xlsx
+++ b/output/pdf_financials_xlsx/GFM.H.xlsx
@@ -1029,13 +1029,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>5e-06</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>2e-06</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3e-06</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.295502</v>
+        <v>-0.295507</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.338749</v>
+        <v>-0.338751</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.236633</v>
+        <v>-0.236636</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.134168</v>
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.295502</v>
+        <v>-0.295507</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.338749</v>
+        <v>-0.338751</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.236633</v>
+        <v>-0.236636</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.134168</v>
@@ -39282,7 +39282,7 @@
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -39991,7 +39991,7 @@
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E324" s="5" t="n">
